--- a/naver_address_auto/주소록.xlsx
+++ b/naver_address_auto/주소록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\naver_address_auto\naver_address_auto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\네이버자동주문\naver_address_auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83915E96-6400-4EE3-AA28-4203981DDA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67253B9-5F01-457C-9146-5A148496B2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3600" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="185">
   <si>
     <t>수취인</t>
   </si>
@@ -582,37 +582,40 @@
   <si>
     <t>ce10171a4c4faf0504</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버아이디</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -657,7 +660,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -986,24 +989,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="55.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.75" style="1" customWidth="1"/>
-    <col min="11" max="23" width="9" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" customWidth="1"/>
+    <col min="12" max="23" width="9" style="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,8 +1038,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1067,7 +1074,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1099,7 +1106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1131,7 +1138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1163,7 +1170,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1195,7 +1202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -1227,7 +1234,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -1259,7 +1266,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -1291,7 +1298,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -1323,7 +1330,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -1355,7 +1362,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -1387,7 +1394,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -1419,7 +1426,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>107</v>
       </c>
@@ -1451,7 +1458,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -1483,7 +1490,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -1515,7 +1522,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>132</v>
       </c>
@@ -1547,7 +1554,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>140</v>
       </c>
@@ -1579,7 +1586,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>148</v>
       </c>
@@ -1611,7 +1618,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>156</v>
       </c>
@@ -1643,7 +1650,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -1675,7 +1682,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="E22" s="5"/>
       <c r="G22" s="7" t="s">
         <v>173</v>
@@ -1687,7 +1694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="E23" s="5"/>
       <c r="G23" s="7" t="s">
         <v>181</v>
@@ -1699,7 +1706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="E24" s="5"/>
       <c r="G24" s="7" t="s">
         <v>182</v>
@@ -1711,7 +1718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="G25" s="7" t="s">
         <v>179</v>
       </c>
@@ -1722,7 +1729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="G26" s="7" t="s">
         <v>183</v>
       </c>
@@ -1733,7 +1740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="E27" s="5"/>
       <c r="G27" s="7" t="s">
         <v>180</v>
@@ -1745,10 +1752,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="G29" s="7"/>
     </row>
   </sheetData>
